--- a/forms/trg/Formulir_TRG_most-rg.xlsx
+++ b/forms/trg/Formulir_TRG_most-rg.xlsx
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTA(Anggota!B5:B29)</f>
+        <f>COUNTA(Anggota!B5:B30)</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!F5:F29)</f>
+        <f>COUNTA(Anggota!F5:F30)</f>
         <v/>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M29"/>
+  <dimension ref="A1:M30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -913,22 +913,22 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Habibie, PhD</t>
+          <t>Prof. M. Aryadi Arsyad, MD, MBiomedSc, Ph.D</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Leader</t>
         </is>
       </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
-          <t>Hasanuddin University</t>
+          <t>Department of Physiology, Faculty of Medicine, Hasanuddin University</t>
         </is>
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Pharmacology and Toxicology</t>
+          <t>Human Physiology</t>
         </is>
       </c>
       <c r="F5" s="12" t="n"/>
@@ -939,7 +939,7 @@
       <c r="K5" s="12" t="n"/>
       <c r="L5" s="11" t="inlineStr">
         <is>
-          <t>57217047207</t>
+          <t>57216437469</t>
         </is>
       </c>
       <c r="M5" s="11" t="inlineStr">
@@ -954,12 +954,12 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Irfan Idris, MD</t>
+          <t>Habibie, PhD</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -969,22 +969,18 @@
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>Cell and Molecular Biology</t>
+          <t>Pharmacology and Toxicology</t>
         </is>
       </c>
       <c r="F6" s="12" t="n"/>
       <c r="G6" s="12" t="n"/>
       <c r="H6" s="12" t="n"/>
       <c r="I6" s="12" t="n"/>
-      <c r="J6" s="11" t="inlineStr">
-        <is>
-          <t>0000-0002-7350-8687</t>
-        </is>
-      </c>
+      <c r="J6" s="12" t="n"/>
       <c r="K6" s="12" t="n"/>
       <c r="L6" s="11" t="inlineStr">
         <is>
-          <t>16636857800</t>
+          <t>57217047207</t>
         </is>
       </c>
       <c r="M6" s="11" t="inlineStr">
@@ -999,12 +995,12 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Aminuddin, MD, M.Nut &amp; Diet, Ph.D</t>
+          <t>Prof. Dr. Irfan Idris, MD</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
@@ -1014,7 +1010,7 @@
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Clinical Nutrition</t>
+          <t>Cell and Molecular Biology</t>
         </is>
       </c>
       <c r="F7" s="12" t="n"/>
@@ -1023,13 +1019,13 @@
       <c r="I7" s="12" t="n"/>
       <c r="J7" s="11" t="inlineStr">
         <is>
-          <t>0000-0001-8564-7847</t>
+          <t>0000-0002-7350-8687</t>
         </is>
       </c>
       <c r="K7" s="12" t="n"/>
       <c r="L7" s="11" t="inlineStr">
         <is>
-          <t>46961024900</t>
+          <t>16636857800</t>
         </is>
       </c>
       <c r="M7" s="11" t="inlineStr">
@@ -1044,12 +1040,12 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Prof. Yulia Yusrini Djabir, Ph.D</t>
+          <t>Aminuddin, MD, M.Nut &amp; Diet, Ph.D</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
@@ -1059,7 +1055,7 @@
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>Clinical Pharmacy</t>
+          <t>Clinical Nutrition</t>
         </is>
       </c>
       <c r="F8" s="12" t="n"/>
@@ -1068,15 +1064,15 @@
       <c r="I8" s="12" t="n"/>
       <c r="J8" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-5891-7247</t>
-        </is>
-      </c>
-      <c r="K8" s="11" t="inlineStr">
-        <is>
-          <t>6018543</t>
-        </is>
-      </c>
-      <c r="L8" s="12" t="n"/>
+          <t>0000-0001-8564-7847</t>
+        </is>
+      </c>
+      <c r="K8" s="12" t="n"/>
+      <c r="L8" s="11" t="inlineStr">
+        <is>
+          <t>46961024900</t>
+        </is>
+      </c>
       <c r="M8" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1089,12 +1085,12 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Andi Ariyandy, MD, Ph.D</t>
+          <t>Prof. Yulia Yusrini Djabir, Ph.D</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
@@ -1104,7 +1100,7 @@
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>Sport Physiology</t>
+          <t>Clinical Pharmacy</t>
         </is>
       </c>
       <c r="F9" s="12" t="n"/>
@@ -1113,12 +1109,12 @@
       <c r="I9" s="12" t="n"/>
       <c r="J9" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-6492-5235</t>
+          <t>0000-0002-5891-7247</t>
         </is>
       </c>
       <c r="K9" s="11" t="inlineStr">
         <is>
-          <t>https://sinta.kemdikbud.go.id/authors/scopusanalysis/6688450</t>
+          <t>6018543</t>
         </is>
       </c>
       <c r="L9" s="12" t="n"/>
@@ -1134,12 +1130,12 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Dr. Ika Yustisia, MD</t>
+          <t>Andi Ariyandy, MD, Ph.D</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
@@ -1149,7 +1145,7 @@
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>Biochemistry</t>
+          <t>Sport Physiology</t>
         </is>
       </c>
       <c r="F10" s="12" t="n"/>
@@ -1158,12 +1154,12 @@
       <c r="I10" s="12" t="n"/>
       <c r="J10" s="11" t="inlineStr">
         <is>
-          <t>0000-0001-7611-968X</t>
+          <t>0000-0002-6492-5235</t>
         </is>
       </c>
       <c r="K10" s="11" t="inlineStr">
         <is>
-          <t>6197511</t>
+          <t>https://sinta.kemdikbud.go.id/authors/scopusanalysis/6688450</t>
         </is>
       </c>
       <c r="L10" s="12" t="n"/>
@@ -1179,22 +1175,22 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Prof. Geoffrey Dobson, Ph.D</t>
+          <t>Dr. Ika Yustisia, MD</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>James Cook University, Australia</t>
+          <t>Hasanuddin University</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>Physiology (Cardiovascular)</t>
+          <t>Biochemistry</t>
         </is>
       </c>
       <c r="F11" s="12" t="n"/>
@@ -1203,10 +1199,14 @@
       <c r="I11" s="12" t="n"/>
       <c r="J11" s="11" t="inlineStr">
         <is>
-          <t>0000-0001-7905-4551</t>
-        </is>
-      </c>
-      <c r="K11" s="12" t="n"/>
+          <t>0000-0001-7611-968X</t>
+        </is>
+      </c>
+      <c r="K11" s="11" t="inlineStr">
+        <is>
+          <t>6197511</t>
+        </is>
+      </c>
       <c r="L11" s="12" t="n"/>
       <c r="M11" s="11" t="inlineStr">
         <is>
@@ -1220,12 +1220,12 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Hayley Letson, PhD</t>
+          <t>Prof. Geoffrey Dobson, Ph.D</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
@@ -1235,7 +1235,7 @@
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>Physiology and Pharmacology</t>
+          <t>Physiology (Cardiovascular)</t>
         </is>
       </c>
       <c r="F12" s="12" t="n"/>
@@ -1244,15 +1244,11 @@
       <c r="I12" s="12" t="n"/>
       <c r="J12" s="11" t="inlineStr">
         <is>
-          <t>0000-0003-0135-134X</t>
+          <t>0000-0001-7905-4551</t>
         </is>
       </c>
       <c r="K12" s="12" t="n"/>
-      <c r="L12" s="11" t="inlineStr">
-        <is>
-          <t>36444958600</t>
-        </is>
-      </c>
+      <c r="L12" s="12" t="n"/>
       <c r="M12" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1265,22 +1261,22 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Dr. Elke Sokoya</t>
+          <t>Hayley Letson, PhD</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>College of Medicine and Public Health, Flinders University</t>
+          <t>James Cook University, Australia</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>Chronic Disease</t>
+          <t>Physiology and Pharmacology</t>
         </is>
       </c>
       <c r="F13" s="12" t="n"/>
@@ -1289,13 +1285,13 @@
       <c r="I13" s="12" t="n"/>
       <c r="J13" s="11" t="inlineStr">
         <is>
-          <t>0000-0001-8509-2044</t>
+          <t>0000-0003-0135-134X</t>
         </is>
       </c>
       <c r="K13" s="12" t="n"/>
       <c r="L13" s="11" t="inlineStr">
         <is>
-          <t>7003727980</t>
+          <t>36444958600</t>
         </is>
       </c>
       <c r="M13" s="11" t="inlineStr">
@@ -1310,22 +1306,22 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Nurul Hidayah</t>
+          <t>Dr. Elke Sokoya</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>Hasanuddin University</t>
+          <t>College of Medicine and Public Health, Flinders University</t>
         </is>
       </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>Master Student</t>
+          <t>Chronic Disease</t>
         </is>
       </c>
       <c r="F14" s="12" t="n"/>
@@ -1334,11 +1330,15 @@
       <c r="I14" s="12" t="n"/>
       <c r="J14" s="11" t="inlineStr">
         <is>
-          <t>0009-0007-5827-4601</t>
+          <t>0000-0001-8509-2044</t>
         </is>
       </c>
       <c r="K14" s="12" t="n"/>
-      <c r="L14" s="12" t="n"/>
+      <c r="L14" s="11" t="inlineStr">
+        <is>
+          <t>7003727980</t>
+        </is>
+      </c>
       <c r="M14" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1351,12 +1351,12 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Andhira Prabawati</t>
+          <t>Nurul Hidayah</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
@@ -1375,7 +1375,7 @@
       <c r="I15" s="12" t="n"/>
       <c r="J15" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-1385-9856</t>
+          <t>0009-0007-5827-4601</t>
         </is>
       </c>
       <c r="K15" s="12" t="n"/>
@@ -1392,12 +1392,12 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>Masyita Nurul Jihad</t>
+          <t>Andhira Prabawati</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
@@ -1416,7 +1416,7 @@
       <c r="I16" s="12" t="n"/>
       <c r="J16" s="11" t="inlineStr">
         <is>
-          <t>0009-0005-5649-0904</t>
+          <t>0000-0002-1385-9856</t>
         </is>
       </c>
       <c r="K16" s="12" t="n"/>
@@ -1433,29 +1433,33 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>Nurhayati</t>
+          <t>Masyita Nurul Jihad</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>Doctoral Student</t>
+          <t>Hasanuddin University</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>MOST-RG Team</t>
+          <t>Master Student</t>
         </is>
       </c>
       <c r="F17" s="12" t="n"/>
       <c r="G17" s="12" t="n"/>
       <c r="H17" s="12" t="n"/>
       <c r="I17" s="12" t="n"/>
-      <c r="J17" s="12" t="n"/>
+      <c r="J17" s="11" t="inlineStr">
+        <is>
+          <t>0009-0005-5649-0904</t>
+        </is>
+      </c>
       <c r="K17" s="12" t="n"/>
       <c r="L17" s="12" t="n"/>
       <c r="M17" s="11" t="inlineStr">
@@ -1468,10 +1472,26 @@
       <c r="A18" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="12" t="n"/>
-      <c r="C18" s="12" t="n"/>
-      <c r="D18" s="12" t="n"/>
-      <c r="E18" s="11" t="n"/>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>Nurhayati</t>
+        </is>
+      </c>
+      <c r="C18" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="D18" s="11" t="inlineStr">
+        <is>
+          <t>Doctoral Student</t>
+        </is>
+      </c>
+      <c r="E18" s="11" t="inlineStr">
+        <is>
+          <t>MOST-RG Team</t>
+        </is>
+      </c>
       <c r="F18" s="12" t="n"/>
       <c r="G18" s="12" t="n"/>
       <c r="H18" s="12" t="n"/>
@@ -1479,7 +1499,11 @@
       <c r="J18" s="12" t="n"/>
       <c r="K18" s="12" t="n"/>
       <c r="L18" s="12" t="n"/>
-      <c r="M18" s="12" t="n"/>
+      <c r="M18" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
@@ -1668,15 +1692,32 @@
       <c r="L29" s="12" t="n"/>
       <c r="M29" s="12" t="n"/>
     </row>
+    <row r="30">
+      <c r="A30" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="12" t="n"/>
+      <c r="C30" s="12" t="n"/>
+      <c r="D30" s="12" t="n"/>
+      <c r="E30" s="11" t="n"/>
+      <c r="F30" s="12" t="n"/>
+      <c r="G30" s="12" t="n"/>
+      <c r="H30" s="12" t="n"/>
+      <c r="I30" s="12" t="n"/>
+      <c r="J30" s="12" t="n"/>
+      <c r="K30" s="12" t="n"/>
+      <c r="L30" s="12" t="n"/>
+      <c r="M30" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
